--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -908,7 +908,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260916095452</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1676,24 +1676,13 @@
     <t>MedicationDispense.substitution.type</t>
   </si>
   <si>
-    <t>Code signifying whether a different drug was dispensed from what was prescribed</t>
+    <t>Type de substitution</t>
   </si>
   <si>
     <t>A code signifying whether a different drug was dispensed from what was prescribed.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="G"/&gt;
-    &lt;display value="Substitution autorisée par un produit générique"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>A coded concept describing whether a different medicinal product may be dispensed other than the product as specified exactly in the prescription.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode|3.0.0</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActSubstanceAdminSubstitutionCode-cisis|20260916095455</t>
   </si>
   <si>
     <t>CombinedMedicationDispense.substitutionMade.code</t>
@@ -1711,16 +1700,28 @@
     <t>Indicates the reason for the substitution (or lack of substitution) from what was prescribed.</t>
   </si>
   <si>
-    <t>A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-substitution-medicament-dispensateur-cisis|20260916095453</t>
   </si>
   <si>
     <t>.reasonCode</t>
   </si>
   <si>
     <t>CombinedMedicationDispense.substitutionMade.reasonCode</t>
+  </si>
+  <si>
+    <t>MedicationDispense.substitution.reason.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.substitution.reason.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.substitution.reason.coding</t>
+  </si>
+  <si>
+    <t>MedicationDispense.substitution.reason.text</t>
+  </si>
+  <si>
+    <t>le motif de substitution / non-substitution</t>
   </si>
   <si>
     <t>MedicationDispense.substitution.responsibleParty</t>
@@ -2098,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.29296875" customWidth="true" bestFit="true"/>
@@ -2126,7 +2127,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.9609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -10714,28 +10715,26 @@
         <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y74" s="2"/>
+      <c r="Z74" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10777,18 +10776,18 @@
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AO74" t="s" s="2">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>542</v>
-      </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10799,10 +10798,10 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -10814,10 +10813,10 @@
         <v>181</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10844,13 +10843,11 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10868,7 +10865,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10886,13 +10883,13 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -10900,10 +10897,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10914,7 +10911,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10926,13 +10923,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>550</v>
+        <v>228</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>551</v>
+        <v>229</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>552</v>
+        <v>230</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10983,31 +10980,31 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>549</v>
+        <v>231</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>553</v>
+        <v>232</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11015,14 +11012,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>556</v>
+        <v>133</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11041,16 +11038,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>557</v>
+        <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>558</v>
+        <v>135</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>559</v>
+        <v>234</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>560</v>
+        <v>137</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11088,19 +11085,19 @@
         <v>78</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>78</v>
+        <v>278</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>555</v>
+        <v>235</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11112,13 +11109,13 @@
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>561</v>
+        <v>232</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11132,10 +11129,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11155,21 +11152,23 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>563</v>
+        <v>281</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>564</v>
+        <v>282</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>565</v>
+        <v>283</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>562</v>
+        <v>287</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11235,20 +11234,488 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="N82" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO82" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO78">
+  <autoFilter ref="A1:AO82">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11258,7 +11725,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/main/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
